--- a/Assets/Resources/Storys/13.xlsx
+++ b/Assets/Resources/Storys/13.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10800" windowHeight="10695"/>
+    <workbookView windowWidth="21600" windowHeight="10695"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1002,10 +1002,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1030,8 +1030,14 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1">
+        <v>1</v>
+      </c>
+      <c r="J1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,7 +1045,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
